--- a/shein - Copy.xlsx
+++ b/shein - Copy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Tool-Buy-Shein\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Tool-buy-Shein\Tool-Buy-Shein\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF270A96-2C8D-40B2-859F-22B5E33FB74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4A9A93-AE39-44F6-A935-977F4969A423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91B14417-4F65-4B5F-82C0-EBB1C5344353}"/>
   </bookViews>
@@ -27,100 +27,22 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>name acc</t>
-  </si>
-  <si>
-    <t>ID ORDER</t>
-  </si>
-  <si>
-    <t>ID Order shein</t>
-  </si>
-  <si>
-    <t>Mail</t>
-  </si>
-  <si>
-    <t>TRACKING</t>
-  </si>
-  <si>
-    <t>Order Status</t>
-  </si>
-  <si>
-    <t>SKU Item</t>
-  </si>
-  <si>
-    <t>BASECOST TRÊN SITE</t>
-  </si>
-  <si>
-    <t>Lãi &gt;10$</t>
-  </si>
-  <si>
-    <t>Est, amount</t>
-  </si>
-  <si>
-    <t>30/03/2026</t>
-  </si>
-  <si>
-    <t>Tawonee Watukins Shop</t>
-  </si>
-  <si>
-    <t>Anastasia McMullen
-United States, Illinois, Woodford, Metamora, 1269 South Woodland Lane
-(+1)3092734061
-Postal Code 61548</t>
-  </si>
-  <si>
-    <t>https://p16-oec-general-useast5.ttcdn-us.com/tos-useast5-i-omjb5zjo8w-tx/5a3fbe35dd1f456da03c164abdbec764~tplv-fhlh96nyum-origin-jpeg.jpeg?dr=12178&amp;t=555f072d&amp;ps=933b5bde&amp;shp=5d781b08&amp;shcp=54477afb&amp;idc=useast5&amp;from=1568152328</t>
-  </si>
-  <si>
-    <t>ADD</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>https://us.shein.com/SHEIN-ICON-Plus-Size-Hippie-Women-Lace-Contrast-Allover-Print-Asymmetric-Hem-Camisole-Top-Suitable-For-Festival-Summer-Vacation-Graduation-Season-And-Back-To-School-p-88677111.html?mallCode=1&amp;main_attr=27_447</t>
   </si>
   <si>
     <t>sz25043044187451434</t>
-  </si>
-  <si>
-    <t>Link image</t>
-  </si>
-  <si>
-    <t>image mockup</t>
-  </si>
-  <si>
-    <t>Base Cost</t>
   </si>
   <si>
     <t>color</t>
@@ -138,29 +60,35 @@
     <t>product_url</t>
   </si>
   <si>
-    <t>shipping_address</t>
+    <t>quantity</t>
   </si>
   <si>
-    <t>quantity</t>
+    <t>sku_code</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>https://us.shein.com/ROMWE-Goth-Women-s-Fashion-Floral-Lace-Underwire-Triangle-Cup-Bra-p-179559662.html?src_identifier=st%3D2%60sc%3DGoth%20Women%27s%20Fashion%20Floral%20Lace%20Underwire%20Triangle%20Cup%20Bra%60sr%3D0%60ps%3D1&amp;src_module=search&amp;src_tab_page_id=page_goods_detail1774834800462&amp;mallCode=1&amp;pageListType=4</t>
+  </si>
+  <si>
+    <t>si25082554047550638</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF707070"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -263,48 +191,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -322,64 +247,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
 </file>
 
 <file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
@@ -706,192 +573,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303B7422-C7A5-42D4-80A4-39AD87A21816}">
   <dimension ref="A1:BX10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="2" width="36.375" customWidth="1"/>
+    <col min="3" max="3" width="49" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="8" max="8" width="42.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-    <col min="14" max="14" width="27.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="18.5703125" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="23.875" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="8" max="8" width="42.25" customWidth="1"/>
+    <col min="9" max="9" width="17.75" customWidth="1"/>
+    <col min="10" max="10" width="20.75" customWidth="1"/>
+    <col min="14" max="14" width="27.25" customWidth="1"/>
+    <col min="15" max="15" width="13.75" customWidth="1"/>
+    <col min="16" max="16" width="18.625" customWidth="1"/>
+    <col min="17" max="17" width="20.75" customWidth="1"/>
+    <col min="18" max="18" width="25.875" customWidth="1"/>
+    <col min="19" max="19" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:76" s="7" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8"/>
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:76" s="7" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="12"/>
+      <c r="AD1" s="12"/>
+      <c r="AE1" s="12"/>
+      <c r="AF1" s="12"/>
+      <c r="AG1" s="12"/>
+      <c r="AH1" s="12"/>
+      <c r="AI1" s="12"/>
+      <c r="AJ1" s="12"/>
+      <c r="AK1" s="12"/>
+      <c r="AL1" s="12"/>
+      <c r="AM1" s="12"/>
+      <c r="AN1" s="12"/>
+      <c r="AO1" s="12"/>
+      <c r="AP1" s="12"/>
+      <c r="AQ1" s="12"/>
+      <c r="AR1" s="12"/>
+      <c r="AS1" s="12"/>
+      <c r="AT1" s="12"/>
+      <c r="AU1" s="12"/>
+      <c r="AV1" s="12"/>
+      <c r="AW1" s="12"/>
+      <c r="AX1" s="12"/>
+      <c r="AY1" s="12"/>
+      <c r="AZ1" s="12"/>
+      <c r="BA1" s="12"/>
+      <c r="BB1" s="12"/>
+      <c r="BC1" s="12"/>
+      <c r="BD1" s="12"/>
+      <c r="BE1" s="12"/>
+      <c r="BF1" s="12"/>
+      <c r="BG1" s="12"/>
+      <c r="BH1" s="12"/>
+      <c r="BI1" s="12"/>
+      <c r="BJ1" s="12"/>
+      <c r="BK1" s="12"/>
+      <c r="BL1" s="12"/>
+      <c r="BM1" s="12"/>
+      <c r="BN1" s="12"/>
+      <c r="BO1" s="12"/>
+      <c r="BP1" s="12"/>
+      <c r="BQ1" s="12"/>
+      <c r="BR1" s="12"/>
+      <c r="BS1" s="12"/>
+      <c r="BT1" s="12"/>
+      <c r="BU1" s="12"/>
+      <c r="BV1" s="12"/>
+      <c r="BW1" s="12"/>
+      <c r="BX1" s="13"/>
+    </row>
+    <row r="2" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D2" s="3" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="S1" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" s="1"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
-      <c r="AJ1" s="13"/>
-      <c r="AK1" s="13"/>
-      <c r="AL1" s="13"/>
-      <c r="AM1" s="13"/>
-      <c r="AN1" s="13"/>
-      <c r="AO1" s="13"/>
-      <c r="AP1" s="13"/>
-      <c r="AQ1" s="13"/>
-      <c r="AR1" s="13"/>
-      <c r="AS1" s="13"/>
-      <c r="AT1" s="13"/>
-      <c r="AU1" s="13"/>
-      <c r="AV1" s="13"/>
-      <c r="AW1" s="13"/>
-      <c r="AX1" s="13"/>
-      <c r="AY1" s="13"/>
-      <c r="AZ1" s="13"/>
-      <c r="BA1" s="13"/>
-      <c r="BB1" s="13"/>
-      <c r="BC1" s="13"/>
-      <c r="BD1" s="13"/>
-      <c r="BE1" s="13"/>
-      <c r="BF1" s="13"/>
-      <c r="BG1" s="13"/>
-      <c r="BH1" s="13"/>
-      <c r="BI1" s="13"/>
-      <c r="BJ1" s="13"/>
-      <c r="BK1" s="13"/>
-      <c r="BL1" s="13"/>
-      <c r="BM1" s="13"/>
-      <c r="BN1" s="13"/>
-      <c r="BO1" s="13"/>
-      <c r="BP1" s="13"/>
-      <c r="BQ1" s="13"/>
-      <c r="BR1" s="13"/>
-      <c r="BS1" s="13"/>
-      <c r="BT1" s="13"/>
-      <c r="BU1" s="13"/>
-      <c r="BV1" s="13"/>
-      <c r="BW1" s="13"/>
-      <c r="BX1" s="14"/>
-    </row>
-    <row r="2" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3">
-        <v>5.7732837717577306E+17</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" s="6">
-        <v>18.52</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>25.15</v>
-      </c>
-      <c r="R2" s="6">
-        <v>48.67</v>
-      </c>
-      <c r="S2" s="6">
-        <v>20.05</v>
-      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
@@ -950,12 +769,22 @@
       <c r="BW2" s="3"/>
       <c r="BX2" s="3"/>
     </row>
-    <row r="3" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
+    <row r="3" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="3"/>
       <c r="H3" s="5"/>
@@ -1028,10 +857,10 @@
       <c r="BW3" s="3"/>
       <c r="BX3" s="3"/>
     </row>
-    <row r="4" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+    <row r="4" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+      <c r="A4" s="4"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="3"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -1106,10 +935,10 @@
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
     </row>
-    <row r="5" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
+    <row r="5" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+      <c r="A5" s="4"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="3"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -1184,7 +1013,7 @@
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
     </row>
-    <row r="6" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1262,7 +1091,7 @@
       <c r="BW6" s="3"/>
       <c r="BX6" s="3"/>
     </row>
-    <row r="7" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1340,7 +1169,7 @@
       <c r="BW7" s="3"/>
       <c r="BX7" s="3"/>
     </row>
-    <row r="8" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1418,7 +1247,7 @@
       <c r="BW8" s="3"/>
       <c r="BX8" s="3"/>
     </row>
-    <row r="9" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1496,7 +1325,7 @@
       <c r="BW9" s="3"/>
       <c r="BX9" s="3"/>
     </row>
-    <row r="10" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>

--- a/shein - Copy.xlsx
+++ b/shein - Copy.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Tool-buy-Shein\Tool-Buy-Shein\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Tool-Buy-Shein\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4A9A93-AE39-44F6-A935-977F4969A423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93D6AB3-22E6-420C-B9E6-CCFCB5E7024E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91B14417-4F65-4B5F-82C0-EBB1C5344353}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91B14417-4F65-4B5F-82C0-EBB1C5344353}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,15 +30,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>https://us.shein.com/SHEIN-ICON-Plus-Size-Hippie-Women-Lace-Contrast-Allover-Print-Asymmetric-Hem-Camisole-Top-Suitable-For-Festival-Summer-Vacation-Graduation-Season-And-Back-To-School-p-88677111.html?mallCode=1&amp;main_attr=27_447</t>
   </si>
@@ -76,13 +74,28 @@
   </si>
   <si>
     <t>si25082554047550638</t>
+  </si>
+  <si>
+    <t>shipping_address</t>
+  </si>
+  <si>
+    <t>summer mazzotta
+United States, Connecticut, Fairfield, Greenwich,20 Church St Apt B50
+(+1)2038323539
+Postal Code 06830</t>
+  </si>
+  <si>
+    <t>Tanner Meagher
+United States, Arizona, Maricopa, Glendale,4551 W Piute Ave
+(+1)6025717450
+Postal Code 85308</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -232,6 +245,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -247,12 +263,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -573,27 +583,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303B7422-C7A5-42D4-80A4-39AD87A21816}">
   <dimension ref="A1:BX10"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.75" customWidth="1"/>
-    <col min="2" max="2" width="36.375" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" customWidth="1"/>
     <col min="3" max="3" width="49" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="23.875" customWidth="1"/>
-    <col min="7" max="7" width="14.75" customWidth="1"/>
-    <col min="8" max="8" width="42.25" customWidth="1"/>
-    <col min="9" max="9" width="17.75" customWidth="1"/>
-    <col min="10" max="10" width="20.75" customWidth="1"/>
-    <col min="14" max="14" width="27.25" customWidth="1"/>
-    <col min="15" max="15" width="13.75" customWidth="1"/>
-    <col min="16" max="16" width="18.625" customWidth="1"/>
-    <col min="17" max="17" width="20.75" customWidth="1"/>
-    <col min="18" max="18" width="25.875" customWidth="1"/>
-    <col min="19" max="19" width="14.625" customWidth="1"/>
+    <col min="6" max="6" width="31.28515625" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="42.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="14" max="14" width="27.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="18.5703125" customWidth="1"/>
+    <col min="17" max="17" width="20.7109375" customWidth="1"/>
+    <col min="18" max="18" width="25.85546875" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:76" s="7" customFormat="1" ht="16.5" thickBot="1">
+    <row r="1" spans="1:76" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>2</v>
       </c>
@@ -609,7 +619,9 @@
       <c r="E1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="8"/>
+      <c r="F1" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
@@ -681,23 +693,25 @@
       <c r="BW1" s="12"/>
       <c r="BX1" s="13"/>
     </row>
-    <row r="2" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="14" t="s">
+        <v>15</v>
+      </c>
       <c r="G2" s="3"/>
       <c r="H2" s="5"/>
       <c r="I2" s="3"/>
@@ -769,23 +783,25 @@
       <c r="BW2" s="3"/>
       <c r="BX2" s="3"/>
     </row>
-    <row r="3" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4">
         <v>1</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="14" t="s">
+        <v>14</v>
+      </c>
       <c r="G3" s="3"/>
       <c r="H3" s="5"/>
       <c r="I3" s="3"/>
@@ -857,13 +873,7 @@
       <c r="BW3" s="3"/>
       <c r="BX3" s="3"/>
     </row>
-    <row r="4" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+    <row r="4" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G4" s="3"/>
       <c r="H4" s="5"/>
       <c r="I4" s="3"/>
@@ -935,7 +945,7 @@
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
     </row>
-    <row r="5" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+    <row r="5" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="3"/>
       <c r="C5" s="5"/>
@@ -1013,7 +1023,7 @@
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
     </row>
-    <row r="6" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+    <row r="6" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1091,7 +1101,7 @@
       <c r="BW6" s="3"/>
       <c r="BX6" s="3"/>
     </row>
-    <row r="7" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+    <row r="7" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1169,7 +1179,7 @@
       <c r="BW7" s="3"/>
       <c r="BX7" s="3"/>
     </row>
-    <row r="8" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+    <row r="8" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1247,7 +1257,7 @@
       <c r="BW8" s="3"/>
       <c r="BX8" s="3"/>
     </row>
-    <row r="9" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+    <row r="9" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1325,7 +1335,7 @@
       <c r="BW9" s="3"/>
       <c r="BX9" s="3"/>
     </row>
-    <row r="10" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
+    <row r="10" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>

--- a/shein - Copy.xlsx
+++ b/shein - Copy.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Tool-Buy-Shein\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93D6AB3-22E6-420C-B9E6-CCFCB5E7024E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE686867-C590-4D48-960E-2729271A0AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91B14417-4F65-4B5F-82C0-EBB1C5344353}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91B14417-4F65-4B5F-82C0-EBB1C5344353}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>https://us.shein.com/SHEIN-ICON-Plus-Size-Hippie-Women-Lace-Contrast-Allover-Print-Asymmetric-Hem-Camisole-Top-Suitable-For-Festival-Summer-Vacation-Graduation-Season-And-Back-To-School-p-88677111.html?mallCode=1&amp;main_attr=27_447</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>sz25043044187451434</t>
   </si>
@@ -55,9 +51,6 @@
     <t>Green</t>
   </si>
   <si>
-    <t>product_url</t>
-  </si>
-  <si>
     <t>quantity</t>
   </si>
   <si>
@@ -68,9 +61,6 @@
   </si>
   <si>
     <t>S</t>
-  </si>
-  <si>
-    <t>https://us.shein.com/ROMWE-Goth-Women-s-Fashion-Floral-Lace-Underwire-Triangle-Cup-Bra-p-179559662.html?src_identifier=st%3D2%60sc%3DGoth%20Women%27s%20Fashion%20Floral%20Lace%20Underwire%20Triangle%20Cup%20Bra%60sr%3D0%60ps%3D1&amp;src_module=search&amp;src_tab_page_id=page_goods_detail1774834800462&amp;mallCode=1&amp;pageListType=4</t>
   </si>
   <si>
     <t>si25082554047550638</t>
@@ -85,10 +75,25 @@
 Postal Code 06830</t>
   </si>
   <si>
-    <t>Tanner Meagher
-United States, Arizona, Maricopa, Glendale,4551 W Piute Ave
-(+1)6025717450
-Postal Code 85308</t>
+    <t>shop_code</t>
+  </si>
+  <si>
+    <t>Norisha Delva
+United States, Florida, Broward, Hollywood, 3800 Hillcrest Dr Apt 504
+(+1)8635135526
+Postal Code 33021</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>si251027234666868624</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -582,45 +587,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303B7422-C7A5-42D4-80A4-39AD87A21816}">
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="36.42578125" customWidth="1"/>
-    <col min="3" max="3" width="49" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="31.28515625" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="8" max="8" width="42.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-    <col min="14" max="14" width="27.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="18.5703125" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="42.28515625" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="13" max="13" width="27.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="18.5703125" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" customWidth="1"/>
+    <col min="17" max="17" width="25.85546875" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:76" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:75" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>2</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>3</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
@@ -630,12 +634,12 @@
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="1"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="12"/>
       <c r="U1" s="12"/>
       <c r="V1" s="12"/>
       <c r="W1" s="12"/>
@@ -690,41 +694,40 @@
       <c r="BT1" s="12"/>
       <c r="BU1" s="12"/>
       <c r="BV1" s="12"/>
-      <c r="BW1" s="12"/>
-      <c r="BX1" s="13"/>
+      <c r="BW1" s="13"/>
     </row>
-    <row r="2" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:75" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="F2" s="3">
         <v>1</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="3"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
+      <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
@@ -781,40 +784,39 @@
       <c r="BU2" s="3"/>
       <c r="BV2" s="3"/>
       <c r="BW2" s="3"/>
-      <c r="BX2" s="3"/>
     </row>
-    <row r="3" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:75" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4">
+        <v>2</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3">
         <v>1</v>
       </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="3"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
+      <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
@@ -871,22 +873,39 @@
       <c r="BU3" s="3"/>
       <c r="BV3" s="3"/>
       <c r="BW3" s="3"/>
-      <c r="BX3" s="3"/>
     </row>
-    <row r="4" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G4" s="3"/>
-      <c r="H4" s="5"/>
+    <row r="4" spans="1:75" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="7">
+        <v>2</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="3"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
+      <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -943,28 +962,39 @@
       <c r="BU4" s="3"/>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
-      <c r="BX4" s="3"/>
     </row>
-    <row r="5" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="5"/>
+    <row r="5" spans="1:75" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="3"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
+      <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
@@ -1021,28 +1051,27 @@
       <c r="BU5" s="3"/>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
-      <c r="BX5" s="3"/>
     </row>
-    <row r="6" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:75" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="5"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="3"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
+      <c r="S6" s="3"/>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
@@ -1099,28 +1128,27 @@
       <c r="BU6" s="3"/>
       <c r="BV6" s="3"/>
       <c r="BW6" s="3"/>
-      <c r="BX6" s="3"/>
     </row>
-    <row r="7" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:75" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="5"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="3"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
+      <c r="S7" s="3"/>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
@@ -1177,28 +1205,27 @@
       <c r="BU7" s="3"/>
       <c r="BV7" s="3"/>
       <c r="BW7" s="3"/>
-      <c r="BX7" s="3"/>
     </row>
-    <row r="8" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:75" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="5"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="3"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="6"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
+      <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
@@ -1255,28 +1282,27 @@
       <c r="BU8" s="3"/>
       <c r="BV8" s="3"/>
       <c r="BW8" s="3"/>
-      <c r="BX8" s="3"/>
     </row>
-    <row r="9" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:75" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="5"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="3"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="6"/>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
+      <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
@@ -1333,28 +1359,27 @@
       <c r="BU9" s="3"/>
       <c r="BV9" s="3"/>
       <c r="BW9" s="3"/>
-      <c r="BX9" s="3"/>
     </row>
-    <row r="10" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:75" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="5"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="3"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="6"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
+      <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
@@ -1411,7 +1436,6 @@
       <c r="BU10" s="3"/>
       <c r="BV10" s="3"/>
       <c r="BW10" s="3"/>
-      <c r="BX10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
